--- a/Result/profitability/2454.xlsx
+++ b/Result/profitability/2454.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM82"/>
+  <dimension ref="A1:AM83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -667,10 +667,10 @@
         <v>6.01</v>
       </c>
       <c r="M2" t="n">
-        <v>14.78125</v>
+        <v>14.69875</v>
       </c>
       <c r="N2" t="n">
-        <v>49.0125</v>
+        <v>48.685</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -776,10 +776,10 @@
         <v>4.95</v>
       </c>
       <c r="M3" t="n">
-        <v>13.4075</v>
+        <v>13.4475</v>
       </c>
       <c r="N3" t="n">
-        <v>49.575</v>
+        <v>49.2825</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -893,10 +893,10 @@
         <v>6.76</v>
       </c>
       <c r="M4" t="n">
-        <v>12.3825</v>
+        <v>11.98875</v>
       </c>
       <c r="N4" t="n">
-        <v>51.3675</v>
+        <v>51.125</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1010,10 +1010,10 @@
         <v>6.96</v>
       </c>
       <c r="M5" t="n">
-        <v>10.94875</v>
+        <v>10.67125</v>
       </c>
       <c r="N5" t="n">
-        <v>52.02375</v>
+        <v>51.65750000000001</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1127,10 +1127,10 @@
         <v>8.15</v>
       </c>
       <c r="M6" t="n">
-        <v>9.780000000000001</v>
+        <v>9.710000000000001</v>
       </c>
       <c r="N6" t="n">
-        <v>53.04625</v>
+        <v>53.005</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1252,10 +1252,10 @@
         <v>7.9</v>
       </c>
       <c r="M7" t="n">
-        <v>8.787500000000001</v>
+        <v>8.897499999999999</v>
       </c>
       <c r="N7" t="n">
-        <v>54.21625</v>
+        <v>54.225</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1377,10 +1377,10 @@
         <v>11.5</v>
       </c>
       <c r="M8" t="n">
-        <v>8.425000000000001</v>
+        <v>8.438749999999999</v>
       </c>
       <c r="N8" t="n">
-        <v>55.5825</v>
+        <v>55.57</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -1883,7 +1883,7 @@
         <v>6.74</v>
       </c>
       <c r="M12" t="n">
-        <v>7.026249999999999</v>
+        <v>7.02625</v>
       </c>
       <c r="N12" t="n">
         <v>54.33875</v>
@@ -2013,7 +2013,7 @@
         <v>6.49375</v>
       </c>
       <c r="N13" t="n">
-        <v>54.23625000000001</v>
+        <v>54.23625</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2267,7 +2267,7 @@
         <v>6.38125</v>
       </c>
       <c r="N15" t="n">
-        <v>54.49124999999999</v>
+        <v>54.49125</v>
       </c>
       <c r="O15" t="n">
         <v>1</v>
@@ -2394,7 +2394,7 @@
         <v>6.3175</v>
       </c>
       <c r="N16" t="n">
-        <v>54.88249999999999</v>
+        <v>54.8825</v>
       </c>
       <c r="O16" t="n">
         <v>1</v>
@@ -2518,7 +2518,7 @@
         <v>8.130000000000001</v>
       </c>
       <c r="M17" t="n">
-        <v>6.5675</v>
+        <v>6.567500000000001</v>
       </c>
       <c r="N17" t="n">
         <v>55.40375</v>
@@ -2645,7 +2645,7 @@
         <v>10.29</v>
       </c>
       <c r="M18" t="n">
-        <v>7.36625</v>
+        <v>7.366249999999999</v>
       </c>
       <c r="N18" t="n">
         <v>56.1425</v>
@@ -3026,7 +3026,7 @@
         <v>3.52</v>
       </c>
       <c r="M21" t="n">
-        <v>7.853750000000001</v>
+        <v>7.85375</v>
       </c>
       <c r="N21" t="n">
         <v>55.91125</v>
@@ -10826,6 +10826,133 @@
       </c>
       <c r="AM82" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>2454</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C83" t="n">
+        <v>152183</v>
+      </c>
+      <c r="D83" t="n">
+        <v>81875</v>
+      </c>
+      <c r="E83" t="n">
+        <v>70308</v>
+      </c>
+      <c r="F83" t="n">
+        <v>46.2</v>
+      </c>
+      <c r="G83" t="n">
+        <v>22868</v>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>15.03%</t>
+        </is>
+      </c>
+      <c r="I83" t="n">
+        <v>5094</v>
+      </c>
+      <c r="J83" t="n">
+        <v>27962</v>
+      </c>
+      <c r="K83" t="n">
+        <v>24335</v>
+      </c>
+      <c r="L83" t="n">
+        <v>15.28</v>
+      </c>
+      <c r="M83" t="n">
+        <v>15.94</v>
+      </c>
+      <c r="N83" t="n">
+        <v>47.47375</v>
+      </c>
+      <c r="O83" t="n">
+        <v>1</v>
+      </c>
+      <c r="P83" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q83" t="n">
+        <v>0</v>
+      </c>
+      <c r="R83" t="n">
+        <v>0</v>
+      </c>
+      <c r="S83" t="n">
+        <v>1</v>
+      </c>
+      <c r="T83" t="n">
+        <v>0</v>
+      </c>
+      <c r="U83" t="n">
+        <v>1</v>
+      </c>
+      <c r="V83" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W83" t="n">
+        <v>0.1099999999999994</v>
+      </c>
+      <c r="X83" t="n">
+        <v>0.007251153592616966</v>
+      </c>
+      <c r="Y83" t="n">
+        <v>-0.09999999999999432</v>
+      </c>
+      <c r="Z83" t="n">
+        <v>-0.002159827213822796</v>
+      </c>
+      <c r="AA83" t="n">
+        <v>-2.220000000000001</v>
+      </c>
+      <c r="AB83" t="n">
+        <v>-0.1268571428571429</v>
+      </c>
+      <c r="AC83" t="n">
+        <v>-2.93</v>
+      </c>
+      <c r="AD83" t="n">
+        <v>-0.05963769590881329</v>
+      </c>
+      <c r="AE83" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF83" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG83" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH83" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI83" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ83" t="inlineStr">
+        <is>
+          <t>EPS衰退 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK83" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL83" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM83" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
